--- a/Chapter-6b/5 - OT - Checklist for Equipment Power and Water Requirements.xlsx
+++ b/Chapter-6b/5 - OT - Checklist for Equipment Power and Water Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\Architecture Manual\3 - Final Version - Under Review\Section 6b - Operation theatre &amp; sterilisation process\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasipriyakarumanchi/Library/CloudStorage/GoogleDrive-sashi@aravind.org/My Drive/Architecture Manual/3 - Final Version - Under Review/Section 6b - Operation theatre &amp; sterilisation process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F32A425-767A-4C0B-AC26-68DC335A4D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6ED5F5-2F63-2C4F-99AC-1D0E35030FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{887F3C2A-6005-4F42-ADB4-3E03998534F5}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{887F3C2A-6005-4F42-ADB4-3E03998534F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Equip - Power-Watts-Water" sheetId="1" r:id="rId1"/>
@@ -111,26 +111,37 @@
     <t>Size - Footprint</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.499984740745262"/>
-        <rFont val="Century Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Section 5b - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Century Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Layout Considerations for Operation Theatre Complex </t>
-    </r>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment </t>
+  </si>
+  <si>
+    <t>Phaco machine</t>
+  </si>
+  <si>
+    <t>Cylinder oxygen</t>
+  </si>
+  <si>
+    <t>Humidity control</t>
+  </si>
+  <si>
+    <t>CCTV</t>
+  </si>
+  <si>
+    <t>S No.</t>
+  </si>
+  <si>
+    <t>Watts</t>
+  </si>
+  <si>
+    <t>Power Supply</t>
+  </si>
+  <si>
+    <t>Stabilised</t>
+  </si>
+  <si>
+    <t>Standardised Architectural Modules for Layouts</t>
   </si>
   <si>
     <r>
@@ -139,7 +150,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color rgb="FFC00000"/>
         <rFont val="Century Gothic"/>
         <family val="2"/>
@@ -147,42 +158,12 @@
       <t>Power and Water and other Supply Requirements for Operation Theatre Complex</t>
     </r>
   </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment </t>
-  </si>
-  <si>
-    <t>Phaco machine</t>
-  </si>
-  <si>
-    <t>Cylinder oxygen</t>
-  </si>
-  <si>
-    <t>Humidity control</t>
-  </si>
-  <si>
-    <t>CCTV</t>
-  </si>
-  <si>
-    <t>S No.</t>
-  </si>
-  <si>
-    <t>Watts</t>
-  </si>
-  <si>
-    <t>Power Supply</t>
-  </si>
-  <si>
-    <t>Stabilised</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,20 +185,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Century Gothic"/>
@@ -233,6 +200,33 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="4" tint="-0.499984740745262"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -703,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -745,13 +739,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -763,8 +757,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
@@ -799,41 +817,23 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,9 +853,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -893,7 +893,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -999,7 +999,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1141,7 +1141,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1153,103 +1153,103 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.04296875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="7.26953125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="5.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="5.40625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="5.58984375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="5.81640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="6.08984375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="6.81640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="6.453125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.26953125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="24.31640625" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.81640625" style="5"/>
+    <col min="1" max="1" width="5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="5.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="6.83203125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="6.5" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="24.33203125" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+    </row>
+    <row r="2" spans="1:14" s="46" customFormat="1" ht="21.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+    </row>
+    <row r="3" spans="1:14" s="6" customFormat="1" ht="29" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="42"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A2" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-    </row>
-    <row r="3" spans="1:14" s="6" customFormat="1" ht="28.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="40" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="6" customFormat="1" ht="77.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A4" s="26"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="32"/>
+    </row>
+    <row r="4" spans="1:14" s="6" customFormat="1" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>19</v>
@@ -1260,18 +1260,18 @@
       <c r="K4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="41"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="21"/>
     </row>
-    <row r="5" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
         <v>1</v>
       </c>
-      <c r="B5" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="39"/>
+      <c r="B5" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="29"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="8"/>
@@ -1283,14 +1283,14 @@
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
     </row>
-    <row r="6" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="37"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="2"/>
@@ -1302,14 +1302,14 @@
       <c r="L6" s="3"/>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16">
         <v>3</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="37"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
       <c r="F7" s="2"/>
@@ -1321,14 +1321,14 @@
       <c r="L7" s="3"/>
       <c r="M7" s="11"/>
     </row>
-    <row r="8" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="37"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
       <c r="F8" s="2"/>
@@ -1340,14 +1340,14 @@
       <c r="L8" s="3"/>
       <c r="M8" s="11"/>
     </row>
-    <row r="9" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16">
         <v>5</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="37"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="2"/>
@@ -1359,14 +1359,14 @@
       <c r="L9" s="3"/>
       <c r="M9" s="11"/>
     </row>
-    <row r="10" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16">
         <v>6</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="37"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="2"/>
@@ -1378,14 +1378,14 @@
       <c r="L10" s="3"/>
       <c r="M10" s="11"/>
     </row>
-    <row r="11" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16">
         <v>7</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="37"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
       <c r="F11" s="2"/>
@@ -1397,14 +1397,14 @@
       <c r="L11" s="3"/>
       <c r="M11" s="11"/>
     </row>
-    <row r="12" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16">
         <v>8</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="37"/>
+      <c r="B12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="25"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="2"/>
@@ -1416,14 +1416,14 @@
       <c r="L12" s="3"/>
       <c r="M12" s="11"/>
     </row>
-    <row r="13" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16">
         <v>9</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="37"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
       <c r="F13" s="2"/>
@@ -1435,14 +1435,14 @@
       <c r="L13" s="3"/>
       <c r="M13" s="11"/>
     </row>
-    <row r="14" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="16">
         <v>10</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="37"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="2"/>
@@ -1454,14 +1454,14 @@
       <c r="L14" s="3"/>
       <c r="M14" s="11"/>
     </row>
-    <row r="15" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16">
         <v>11</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="37"/>
+      <c r="C15" s="25"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="2"/>
@@ -1473,14 +1473,14 @@
       <c r="L15" s="3"/>
       <c r="M15" s="11"/>
     </row>
-    <row r="16" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16">
         <v>12</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="37"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
       <c r="F16" s="2"/>
@@ -1492,14 +1492,14 @@
       <c r="L16" s="3"/>
       <c r="M16" s="11"/>
     </row>
-    <row r="17" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="16">
         <v>13</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="37"/>
+      <c r="B17" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="25"/>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
       <c r="F17" s="2"/>
@@ -1511,14 +1511,14 @@
       <c r="L17" s="3"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="16">
         <v>14</v>
       </c>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="37"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
       <c r="F18" s="2"/>
@@ -1530,14 +1530,14 @@
       <c r="L18" s="3"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="16">
         <v>15</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="37"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
       <c r="F19" s="2"/>
@@ -1549,14 +1549,14 @@
       <c r="L19" s="3"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="16">
         <v>16</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="25"/>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
       <c r="F20" s="2"/>
@@ -1568,14 +1568,14 @@
       <c r="L20" s="3"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="16">
         <v>17</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="37"/>
+      <c r="C21" s="25"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="2"/>
@@ -1587,14 +1587,14 @@
       <c r="L21" s="3"/>
       <c r="M21" s="11"/>
     </row>
-    <row r="22" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="16">
         <v>18</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="37"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
       <c r="F22" s="2"/>
@@ -1606,14 +1606,14 @@
       <c r="L22" s="3"/>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="16">
         <v>19</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="37"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="2"/>
@@ -1625,14 +1625,14 @@
       <c r="L23" s="3"/>
       <c r="M23" s="11"/>
     </row>
-    <row r="24" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="16">
         <v>20</v>
       </c>
-      <c r="B24" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="37"/>
+      <c r="B24" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="25"/>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="2"/>
@@ -1644,14 +1644,14 @@
       <c r="L24" s="3"/>
       <c r="M24" s="11"/>
     </row>
-    <row r="25" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="25" spans="1:13" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>21</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="43"/>
+      <c r="C25" s="27"/>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="12"/>
@@ -1663,9 +1663,25 @@
       <c r="L25" s="13"/>
       <c r="M25" s="14"/>
     </row>
-    <row r="26" spans="1:13" ht="16.25" thickTop="1" x14ac:dyDescent="0.75"/>
+    <row r="26" spans="1:13" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
@@ -1682,22 +1698,6 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" r:id="rId1"/>
